--- a/output/Q1_2026_Earnings_Dashboard.xlsx
+++ b/output/Q1_2026_Earnings_Dashboard.xlsx
@@ -18,13 +18,177 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F6" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="567">
   <si>
     <t>Summary — FactSet Key Metrics</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 1</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 1</t>
   </si>
   <si>
     <t>Metric</t>
@@ -93,7 +257,7 @@
     <t>Sector Matrix — All 11 GICS Sectors</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 4–7, 14–15, 22–23</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 4–7, 14–15, 22–23</t>
   </si>
   <si>
     <t>Sector</t>
@@ -153,10 +317,16 @@
     <t>Utilities</t>
   </si>
   <si>
+    <t>— means the value isn't published in this week's FactSet PDF. FactSet's narrative spotlights only 5–6 sectors per metric.</t>
+  </si>
+  <si>
+    <t>Italicized cells (with hover note) were extracted via OCR from the all-11-sector bar charts on pages 17/20/22.</t>
+  </si>
+  <si>
     <t>Sector Detail — Industry-Level Earnings &amp; Revenue Growth</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 4, 6</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 4, 6</t>
   </si>
   <si>
     <t>Industry</t>
@@ -240,7 +410,7 @@
     <t>Company Contributors — FactSet-Cited Companies and Ex-Contributor Sensitivity</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 4, 11–13</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 4, 11–13</t>
   </si>
   <si>
     <t>Company / Industry</t>
@@ -294,7 +464,7 @@
     <t>Earnings &amp; Revenue Growth Revisions</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 8–10</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 8–10</t>
   </si>
   <si>
     <t>Index-level growth-rate revisions</t>
@@ -327,7 +497,7 @@
     <t>Market Reaction — Avg Price Move (2-day pre to 2-day post)</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 12–13</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 12–13</t>
   </si>
   <si>
     <t>Surprise type</t>
@@ -345,7 +515,7 @@
     <t>Forward Estimates &amp; EPS Guidance</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 17–21</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 17–21</t>
   </si>
   <si>
     <t>Forward growth &amp; margin estimates</t>
@@ -405,7 +575,7 @@
     <t>Valuation, Price Targets, and Ratings</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: 24–30</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: 24–30</t>
   </si>
   <si>
     <t>Index-level valuation</t>
@@ -465,7 +635,7 @@
     <t>Raw Data — Every Parsed Value</t>
   </si>
   <si>
-    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-27   |   Source pages: all</t>
+    <t>Source: EarningsInsight_042426.pdf   |   FactSet as-of: April 24, 2026   |   Quarter: Q1 2026   |   Parsed: 2026-04-28   |   Source pages: all</t>
   </si>
   <si>
     <t>Path</t>
@@ -498,7 +668,7 @@
     <t>meta.parsedAt</t>
   </si>
   <si>
-    <t>2026-04-27T04:48:24.068Z</t>
+    <t>2026-04-28T05:26:13.541Z</t>
   </si>
   <si>
     <t>meta.pageCount</t>
@@ -916,6 +1086,249 @@
   </si>
   <si>
     <t>sectorMatrix[10].netProfitMarginYearAgo</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.revBeatPct</t>
+  </si>
+  <si>
+    <t>narrative</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Communication Services.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.earningsGrowth</t>
+  </si>
+  <si>
+    <t>chart-p20</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Discretionary.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.epsSurprise</t>
+  </si>
+  <si>
+    <t>chart-p17</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Consumer Staples.netProfitMargin</t>
+  </si>
+  <si>
+    <t>chart-p22</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Energy.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Financials.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Health Care.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Industrials.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Information Technology.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Materials.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Real Estate.netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.epsBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrixSource.Utilities.netProfitMargin</t>
   </si>
   <si>
     <t>sectorIndustries.Communication Services.revenue[0].industry</t>
@@ -1477,7 +1890,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1500,6 +1913,14 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <i/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1547,7 +1968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1556,6 +1977,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2186,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2296,11 +2719,11 @@
       <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>8</v>
+      <c r="E6" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2.4</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>8</v>
@@ -2325,20 +2748,20 @@
       <c r="C7" s="4">
         <v>100</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
+      <c r="D7" s="6">
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>8</v>
+      <c r="F7" s="6">
+        <v>2.7</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>8</v>
+      <c r="H7" s="6">
+        <v>5.9</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>8</v>
@@ -2351,8 +2774,8 @@
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
+      <c r="B8" s="4">
+        <v>100</v>
       </c>
       <c r="C8" s="4">
         <v>100</v>
@@ -2360,14 +2783,14 @@
       <c r="D8" s="4">
         <v>12.7</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>8</v>
+      <c r="E8" s="6">
+        <v>2.8</v>
       </c>
       <c r="F8" s="4">
         <v>-14.4</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>8</v>
+      <c r="G8" s="6">
+        <v>3.8</v>
       </c>
       <c r="H8" s="4">
         <v>6.6</v>
@@ -2389,8 +2812,8 @@
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>8</v>
+      <c r="D9" s="6">
+        <v>6.7</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>8</v>
@@ -2401,8 +2824,8 @@
       <c r="G9" s="4">
         <v>10.8</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>8</v>
+      <c r="H9" s="6">
+        <v>20.2</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>8</v>
@@ -2415,14 +2838,14 @@
       <c r="A10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
+      <c r="B10" s="4">
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>8</v>
+      <c r="D10" s="6">
+        <v>5.7</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>8</v>
@@ -2433,8 +2856,8 @@
       <c r="G10" s="4">
         <v>6.2</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>8</v>
+      <c r="H10" s="6">
+        <v>7.5</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>8</v>
@@ -2465,8 +2888,8 @@
       <c r="G11" s="4">
         <v>6.9</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>8</v>
+      <c r="H11" s="6">
+        <v>11.1</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>8</v>
@@ -2526,11 +2949,11 @@
       <c r="F13" s="4">
         <v>33.1</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>8</v>
+      <c r="G13" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="H13" s="6">
+        <v>10.2</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>8</v>
@@ -2549,20 +2972,20 @@
       <c r="C14" s="4">
         <v>100</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>8</v>
+      <c r="D14" s="6">
+        <v>7.1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.3</v>
+      </c>
+      <c r="F14" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="G14" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="H14" s="6">
+        <v>33.7</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>8</v>
@@ -2581,20 +3004,20 @@
       <c r="C15" s="4">
         <v>67</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>8</v>
+      <c r="D15" s="6">
+        <v>5.8</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>8</v>
+      <c r="F15" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="G15" s="6">
+        <v>8.2</v>
+      </c>
+      <c r="H15" s="6">
+        <v>15.1</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>8</v>
@@ -2602,12 +3025,42 @@
       <c r="J15" s="4" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J15"/>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B15">
     <cfRule type="dataBar" priority="1">
@@ -2618,7 +3071,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38F6D62D-D28A-4D97-9D67-C0813F1564CA}</x14:id>
+          <x14:id>{8D0FC7D1-8456-46CC-B03F-45C241E02ECA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2632,7 +3085,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1A1315C4-D02B-44AB-B77D-BF4ACD2B32FF}</x14:id>
+          <x14:id>{55366F1E-A9FD-4AC6-81FA-3653FA117B07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2646,7 +3099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C58617C3-A1EB-4B85-94A3-61CDBA3D9A58}</x14:id>
+          <x14:id>{075E4C2A-3FB0-4F06-AFDA-F09C6ACDB2B1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2660,7 +3113,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{444B73DA-A55C-426B-ACA5-D9D56EADEF86}</x14:id>
+          <x14:id>{9329AF12-238B-49C3-A081-DFCBA2CA4D43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2674,7 +3127,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6B9744FF-6CC7-4502-ACC0-CE5F780E015F}</x14:id>
+          <x14:id>{5DBB4FA6-F4D4-4F83-9B32-029A67ABEF2B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2688,7 +3141,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D4A51957-8067-467E-B707-BF236325705B}</x14:id>
+          <x14:id>{A996EF0C-CF84-4497-A21A-AF0DCDF2CD18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2702,7 +3155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75AF88B2-F747-4E1A-99F2-A63DD47C2BDF}</x14:id>
+          <x14:id>{D3693E62-54D1-4D55-8BCA-AD9F84A25AC3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2716,7 +3169,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6E363E35-AE42-4F90-A271-D8D9BD86193C}</x14:id>
+          <x14:id>{1E072F38-9FB1-4711-ABA1-50DD73538191}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2730,7 +3183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EF19E7A1-0BE9-4F34-B03B-64E55DE49C64}</x14:id>
+          <x14:id>{CCD2DD5E-484A-4EF1-9DAF-F607CD37D61C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2741,7 +3194,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38F6D62D-D28A-4D97-9D67-C0813F1564CA}">
+          <x14:cfRule type="dataBar" id="{8D0FC7D1-8456-46CC-B03F-45C241E02ECA}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2750,7 +3203,7 @@
           <xm:sqref>B5:B15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1A1315C4-D02B-44AB-B77D-BF4ACD2B32FF}">
+          <x14:cfRule type="dataBar" id="{55366F1E-A9FD-4AC6-81FA-3653FA117B07}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2759,7 +3212,7 @@
           <xm:sqref>C5:C15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C58617C3-A1EB-4B85-94A3-61CDBA3D9A58}">
+          <x14:cfRule type="dataBar" id="{075E4C2A-3FB0-4F06-AFDA-F09C6ACDB2B1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2768,7 +3221,7 @@
           <xm:sqref>D5:D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{444B73DA-A55C-426B-ACA5-D9D56EADEF86}">
+          <x14:cfRule type="dataBar" id="{9329AF12-238B-49C3-A081-DFCBA2CA4D43}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2777,7 +3230,7 @@
           <xm:sqref>E5:E15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6B9744FF-6CC7-4502-ACC0-CE5F780E015F}">
+          <x14:cfRule type="dataBar" id="{5DBB4FA6-F4D4-4F83-9B32-029A67ABEF2B}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2786,7 +3239,7 @@
           <xm:sqref>F5:F15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D4A51957-8067-467E-B707-BF236325705B}">
+          <x14:cfRule type="dataBar" id="{A996EF0C-CF84-4497-A21A-AF0DCDF2CD18}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2795,7 +3248,7 @@
           <xm:sqref>G5:G15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75AF88B2-F747-4E1A-99F2-A63DD47C2BDF}">
+          <x14:cfRule type="dataBar" id="{D3693E62-54D1-4D55-8BCA-AD9F84A25AC3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2804,7 +3257,7 @@
           <xm:sqref>H5:H15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6E363E35-AE42-4F90-A271-D8D9BD86193C}">
+          <x14:cfRule type="dataBar" id="{1E072F38-9FB1-4711-ABA1-50DD73538191}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2813,7 +3266,7 @@
           <xm:sqref>I5:I15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EF19E7A1-0BE9-4F34-B03B-64E55DE49C64}">
+          <x14:cfRule type="dataBar" id="{CCD2DD5E-484A-4EF1-9DAF-F607CD37D61C}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2824,6 +3277,7 @@
       </x14:conditionalFormattings>
     </ext>
   </extLst>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2840,7 +3294,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2852,7 +3306,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2867,13 +3321,13 @@
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,10 +3335,10 @@
         <v>33</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="4">
         <v>21</v>
@@ -2895,10 +3349,10 @@
         <v>33</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" s="4">
         <v>10</v>
@@ -2909,10 +3363,10 @@
         <v>33</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="D7" s="4">
         <v>7</v>
@@ -2923,10 +3377,10 @@
         <v>33</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
@@ -2937,10 +3391,10 @@
         <v>33</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="4">
         <v>2</v>
@@ -2951,7 +3405,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
@@ -2965,7 +3419,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
@@ -2979,10 +3433,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" s="4">
         <v>-46</v>
@@ -2993,10 +3447,10 @@
         <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" s="4">
         <v>-9</v>
@@ -3007,10 +3461,10 @@
         <v>37</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="4">
         <v>34</v>
@@ -3021,10 +3475,10 @@
         <v>37</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" s="4">
         <v>33</v>
@@ -3035,10 +3489,10 @@
         <v>37</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" s="4">
         <v>21</v>
@@ -3049,10 +3503,10 @@
         <v>37</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D17" s="4">
         <v>16</v>
@@ -3063,10 +3517,10 @@
         <v>37</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" s="4">
         <v>9</v>
@@ -3077,10 +3531,10 @@
         <v>37</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4">
         <v>23</v>
@@ -3091,10 +3545,10 @@
         <v>37</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D20" s="4">
         <v>15</v>
@@ -3105,10 +3559,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="4">
         <v>11</v>
@@ -3119,10 +3573,10 @@
         <v>37</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" s="4">
         <v>10</v>
@@ -3133,10 +3587,10 @@
         <v>37</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" s="4">
         <v>6</v>
@@ -3147,10 +3601,10 @@
         <v>38</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D24" s="4">
         <v>-31</v>
@@ -3161,7 +3615,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
@@ -3175,10 +3629,10 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26" s="4">
         <v>98</v>
@@ -3189,10 +3643,10 @@
         <v>40</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D27" s="4">
         <v>33</v>
@@ -3203,10 +3657,10 @@
         <v>40</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
@@ -3217,10 +3671,10 @@
         <v>40</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D29" s="4">
         <v>18</v>
@@ -3234,7 +3688,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D30" s="4">
         <v>14</v>
@@ -3245,10 +3699,10 @@
         <v>40</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D31" s="4">
         <v>7</v>
@@ -3259,10 +3713,10 @@
         <v>40</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D32" s="4">
         <v>51</v>
@@ -3273,10 +3727,10 @@
         <v>40</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D33" s="4">
         <v>27</v>
@@ -3287,10 +3741,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D34" s="4">
         <v>21</v>
@@ -3301,10 +3755,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D35" s="4">
         <v>17</v>
@@ -3315,10 +3769,10 @@
         <v>40</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D36" s="4">
         <v>14</v>
@@ -3329,10 +3783,10 @@
         <v>40</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D37" s="4">
         <v>8</v>
@@ -3343,10 +3797,10 @@
         <v>41</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D38" s="4">
         <v>133</v>
@@ -3357,10 +3811,10 @@
         <v>41</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D39" s="4">
         <v>5</v>
@@ -3371,7 +3825,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>8</v>
@@ -3385,7 +3839,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
@@ -3409,7 +3863,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8E01B2A8-809C-4686-81EE-680C4F0F427B}</x14:id>
+          <x14:id>{88D5E966-A3B9-4D66-BF2A-2B643B4538FC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3420,7 +3874,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8E01B2A8-809C-4686-81EE-680C4F0F427B}">
+          <x14:cfRule type="dataBar" id="{88D5E966-A3B9-4D66-BF2A-2B643B4538FC}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3447,7 +3901,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3459,7 +3913,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3474,16 +3928,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3491,7 +3945,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -3508,7 +3962,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
@@ -3525,7 +3979,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
@@ -3542,7 +3996,7 @@
         <v>36</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4">
         <v>0.97</v>
@@ -3551,7 +4005,7 @@
         <v>1.76</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3559,7 +4013,7 @@
         <v>37</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
@@ -3576,7 +4030,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="4">
         <v>-1.47</v>
@@ -3585,7 +4039,7 @@
         <v>2.22</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3593,7 +4047,7 @@
         <v>39</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" s="4">
         <v>17.44</v>
@@ -3602,7 +4056,7 @@
         <v>1.07</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3610,7 +4064,7 @@
         <v>40</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4">
         <v>1.74</v>
@@ -3619,7 +4073,7 @@
         <v>0.81</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3627,7 +4081,7 @@
         <v>40</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4">
         <v>12.2</v>
@@ -3644,7 +4098,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
@@ -3653,7 +4107,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3661,7 +4115,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>8</v>
@@ -3678,7 +4132,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
@@ -3712,7 +4166,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3724,7 +4178,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3736,7 +4190,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -3750,15 +4204,15 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B6" s="4">
         <v>15.1</v>
@@ -3772,7 +4226,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" s="4">
         <v>10.3</v>
@@ -3786,7 +4240,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -3797,13 +4251,13 @@
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3976,7 +4430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65079CB5-DFAA-4A0F-8A7E-C686EBA5BB1F}</x14:id>
+          <x14:id>{78F4E6A3-F20D-4668-A68B-B0BD4FCB65E2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3990,7 +4444,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50A79245-2E1E-418F-925C-B0E2CD03D9B2}</x14:id>
+          <x14:id>{3EF8189F-EDB4-4252-B25A-E90BEE6A584F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4004,7 +4458,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B677AB4F-28C3-4D2C-9D8D-DC8AE4C38E06}</x14:id>
+          <x14:id>{F9E625A1-AFB2-42B2-B718-011102F69CEA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4015,7 +4469,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{65079CB5-DFAA-4A0F-8A7E-C686EBA5BB1F}">
+          <x14:cfRule type="dataBar" id="{78F4E6A3-F20D-4668-A68B-B0BD4FCB65E2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -4024,7 +4478,7 @@
           <xm:sqref>B11:B21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50A79245-2E1E-418F-925C-B0E2CD03D9B2}">
+          <x14:cfRule type="dataBar" id="{3EF8189F-EDB4-4252-B25A-E90BEE6A584F}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -4033,7 +4487,7 @@
           <xm:sqref>C11:C21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B677AB4F-28C3-4D2C-9D8D-DC8AE4C38E06}">
+          <x14:cfRule type="dataBar" id="{F9E625A1-AFB2-42B2-B718-011102F69CEA}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -4058,7 +4512,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4070,7 +4524,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4082,18 +4536,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" s="4">
         <v>0.9</v>
@@ -4104,7 +4558,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4">
         <v>-2.6</v>
@@ -4135,7 +4589,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4147,7 +4601,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4159,7 +4613,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -4167,7 +4621,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>28</v>
@@ -4181,7 +4635,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4">
         <v>20.6</v>
@@ -4195,7 +4649,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4">
         <v>22.7</v>
@@ -4209,7 +4663,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="4">
         <v>20.4</v>
@@ -4223,7 +4677,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="4">
         <v>18.6</v>
@@ -4237,7 +4691,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>8</v>
@@ -4251,7 +4705,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -4262,18 +4716,18 @@
         <v>2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B14" s="4">
         <v>20</v>
@@ -4287,7 +4741,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B15" s="4">
         <v>11</v>
@@ -4301,7 +4755,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B16" s="4">
         <v>9</v>
@@ -4315,7 +4769,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B17" s="4">
         <v>55</v>
@@ -4329,7 +4783,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -4340,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -4351,7 +4805,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>8</v>
@@ -4388,7 +4842,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4400,7 +4854,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4412,7 +4866,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -4433,12 +4887,12 @@
         <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B6" s="4">
         <v>20.9</v>
@@ -4455,7 +4909,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B7" s="4">
         <v>28.1</v>
@@ -4472,7 +4926,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -4484,7 +4938,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>21</v>
@@ -4685,7 +5139,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -4694,7 +5148,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B24" s="4">
         <v>8362.16</v>
@@ -4711,7 +5165,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B25" s="4">
         <v>7108.4</v>
@@ -4728,7 +5182,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B26" s="4">
         <v>17.6</v>
@@ -4745,7 +5199,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -4757,7 +5211,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>21</v>
@@ -4958,7 +5412,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -4970,7 +5424,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
@@ -4984,7 +5438,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B44" s="4">
         <v>12941</v>
@@ -5001,7 +5455,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B45" s="4">
         <v>58.4</v>
@@ -5018,7 +5472,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B46" s="4">
         <v>36.3</v>
@@ -5035,7 +5489,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B47" s="4">
         <v>5.3</v>
@@ -5052,7 +5506,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -5064,7 +5518,7 @@
         <v>25</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
@@ -5283,7 +5737,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5C581916-ECE8-4036-BDEB-037B7DF4102D}</x14:id>
+          <x14:id>{A6C52E82-D275-4B44-92FE-4E311EBBB9A9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5297,7 +5751,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7FA16161-A34B-42C4-92D2-61ED6B6B6E3B}</x14:id>
+          <x14:id>{62764D28-F051-46D1-A12A-436F2056CBE7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5311,7 +5765,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2DB9B3E4-EC75-4D8D-87CC-7195806EDC71}</x14:id>
+          <x14:id>{CB51F138-8304-4341-BA04-BE514D943690}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5322,7 +5776,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5C581916-ECE8-4036-BDEB-037B7DF4102D}">
+          <x14:cfRule type="dataBar" id="{A6C52E82-D275-4B44-92FE-4E311EBBB9A9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -5331,7 +5785,7 @@
           <xm:sqref>B11:B21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7FA16161-A34B-42C4-92D2-61ED6B6B6E3B}">
+          <x14:cfRule type="dataBar" id="{62764D28-F051-46D1-A12A-436F2056CBE7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -5340,7 +5794,7 @@
           <xm:sqref>B30:B40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2DB9B3E4-EC75-4D8D-87CC-7195806EDC71}">
+          <x14:cfRule type="dataBar" id="{CB51F138-8304-4341-BA04-BE514D943690}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -5356,7 +5810,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H407"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -5365,7 +5819,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5377,7 +5831,7 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5389,3599 +5843,4446 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B9" s="4">
         <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B10" s="4">
         <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B11" s="4">
         <v>84</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B12" s="4">
         <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" s="4">
         <v>15.1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B14" s="4">
         <v>10.3</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" s="4">
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B16" s="4">
         <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B17" s="4">
         <v>20.9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B18" s="4">
         <v>19.9</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B19" s="4">
         <v>18.9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B20" s="4">
         <v>84</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B21" s="4">
         <v>79</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B22" s="4">
         <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B23" s="4">
         <v>76</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B24" s="4">
         <v>12.3</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B25" s="4">
         <v>7.2</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B26" s="4">
         <v>7.3</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B27" s="4">
         <v>7.1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B28" s="4">
         <v>81</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B29" s="4">
         <v>73</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B30" s="4">
         <v>70</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B31" s="4">
         <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B32" s="4">
         <v>2</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B33" s="4">
         <v>1.6</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B34" s="4">
         <v>2</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B35" s="4">
         <v>1.5</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B38" s="4">
         <v>100</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B39" s="4">
         <v>20.6</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B41" s="4">
         <v>-0.2</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B42" s="4">
         <v>13.2</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B43" s="4">
         <v>14.1</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B45" s="4">
         <v>16</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B47" s="4">
         <v>69</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B48" s="4">
         <v>69</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>8</v>
+        <v>205</v>
+      </c>
+      <c r="B50" s="4">
+        <v>0.4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>8</v>
+        <v>206</v>
+      </c>
+      <c r="B51" s="4">
+        <v>2.4</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B58" s="4">
         <v>100</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>8</v>
+        <v>214</v>
+      </c>
+      <c r="B59" s="4">
+        <v>3</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>8</v>
+        <v>216</v>
+      </c>
+      <c r="B61" s="4">
+        <v>2.7</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>8</v>
+        <v>218</v>
+      </c>
+      <c r="B63" s="4">
+        <v>5.9</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>8</v>
+        <v>222</v>
+      </c>
+      <c r="B67" s="4">
+        <v>100</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B68" s="4">
         <v>100</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B69" s="4">
         <v>12.7</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>8</v>
+        <v>225</v>
+      </c>
+      <c r="B70" s="4">
+        <v>2.8</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B71" s="4">
         <v>-14.4</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>8</v>
+        <v>227</v>
+      </c>
+      <c r="B72" s="4">
+        <v>3.8</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B73" s="4">
         <v>6.6</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B74" s="4">
         <v>9.6</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>8</v>
+        <v>234</v>
+      </c>
+      <c r="B79" s="4">
+        <v>6.7</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B81" s="4">
         <v>19.8</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B82" s="4">
         <v>10.8</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>8</v>
+        <v>238</v>
+      </c>
+      <c r="B83" s="4">
+        <v>20.2</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>8</v>
+        <v>242</v>
+      </c>
+      <c r="B87" s="4">
+        <v>100</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>8</v>
+        <v>244</v>
+      </c>
+      <c r="B89" s="4">
+        <v>5.7</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B91" s="4">
         <v>-8.7</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B92" s="4">
         <v>6.2</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>8</v>
+        <v>248</v>
+      </c>
+      <c r="B93" s="4">
+        <v>7.5</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B99" s="4">
         <v>33.2</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B101" s="4">
         <v>16.7</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B102" s="4">
         <v>6.9</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>8</v>
+        <v>258</v>
+      </c>
+      <c r="B103" s="4">
+        <v>11.1</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B107" s="4">
         <v>93</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B109" s="4">
         <v>21.1</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B111" s="4">
         <v>46.3</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B112" s="4">
         <v>28.1</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B113" s="4">
         <v>29.1</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B114" s="4">
         <v>25.3</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B115" s="4">
         <v>25.4</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B119" s="4">
         <v>28.5</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B120" s="4">
         <v>4.4</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B121" s="4">
         <v>33.1</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>8</v>
+        <v>277</v>
+      </c>
+      <c r="B122" s="4">
+        <v>6.9</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>8</v>
+        <v>278</v>
+      </c>
+      <c r="B123" s="4">
+        <v>10.2</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B127" s="4">
         <v>100</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B128" s="4">
         <v>100</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>8</v>
+        <v>284</v>
+      </c>
+      <c r="B129" s="4">
+        <v>7.1</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>8</v>
+        <v>285</v>
+      </c>
+      <c r="B130" s="4">
+        <v>2.3</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>8</v>
+        <v>286</v>
+      </c>
+      <c r="B131" s="4">
+        <v>5.2</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>8</v>
+        <v>287</v>
+      </c>
+      <c r="B132" s="4">
+        <v>9.6</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>8</v>
+        <v>288</v>
+      </c>
+      <c r="B133" s="4">
+        <v>33.7</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B137" s="4">
         <v>100</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B138" s="4">
         <v>67</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>8</v>
+        <v>294</v>
+      </c>
+      <c r="B139" s="4">
+        <v>5.8</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>8</v>
+        <v>296</v>
+      </c>
+      <c r="B141" s="4">
+        <v>11.9</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>8</v>
+        <v>297</v>
+      </c>
+      <c r="B142" s="4">
+        <v>8.2</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>8</v>
+        <v>298</v>
+      </c>
+      <c r="B143" s="4">
+        <v>15.1</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B147" s="4">
-        <v>21</v>
+        <v>302</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>50</v>
+        <v>303</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B149" s="4">
-        <v>10</v>
+        <v>305</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B150" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="C150" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B151" s="4">
-        <v>7</v>
+        <v>307</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>52</v>
+        <v>303</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B153" s="4">
-        <v>4</v>
+        <v>309</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>53</v>
+        <v>303</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B155" s="4">
-        <v>2</v>
+        <v>311</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B157" s="4">
-        <v>-46</v>
+        <v>313</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B159" s="4">
-        <v>-9</v>
+        <v>316</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B161" s="4">
-        <v>34</v>
+        <v>318</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B163" s="4">
-        <v>33</v>
+        <v>321</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B165" s="4">
-        <v>21</v>
+        <v>323</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B167" s="4">
-        <v>16</v>
+        <v>326</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>62</v>
+        <v>303</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B169" s="4">
-        <v>9</v>
+        <v>328</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B171" s="4">
-        <v>23</v>
+        <v>330</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B173" s="4">
-        <v>15</v>
+        <v>332</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B175" s="4">
-        <v>11</v>
+        <v>334</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>61</v>
+        <v>320</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B177" s="4">
-        <v>10</v>
+        <v>336</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B179" s="4">
-        <v>6</v>
+        <v>338</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>63</v>
+        <v>325</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B181" s="4">
-        <v>-31</v>
+        <v>340</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B183" s="4">
-        <v>98</v>
+        <v>342</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B185" s="4">
-        <v>33</v>
+        <v>344</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>66</v>
+        <v>303</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B187" s="4">
-        <v>27</v>
+        <v>346</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B189" s="4">
-        <v>18</v>
+        <v>348</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>33</v>
+        <v>303</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B191" s="4">
-        <v>14</v>
+        <v>350</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>68</v>
+        <v>303</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B193" s="4">
-        <v>7</v>
+        <v>352</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>64</v>
+        <v>325</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B195" s="4">
-        <v>51</v>
+        <v>354</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B197" s="4">
-        <v>27</v>
+        <v>356</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B199" s="4">
-        <v>21</v>
+        <v>358</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>67</v>
+        <v>303</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B201" s="4">
-        <v>17</v>
+        <v>360</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B203" s="4">
-        <v>14</v>
+        <v>362</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>68</v>
+        <v>303</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B205" s="4">
-        <v>8</v>
+        <v>364</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B207" s="4">
-        <v>133</v>
+        <v>366</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="B209" s="4">
-        <v>5</v>
+        <v>368</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="B211" s="4">
-        <v>0.97</v>
+        <v>370</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B212" s="4">
-        <v>1.76</v>
+        <v>371</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B214" s="4">
-        <v>-0.2</v>
+        <v>373</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B215" s="4">
-        <v>-14.4</v>
+        <v>374</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B217" s="4">
-        <v>-1.47</v>
+        <v>376</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B218" s="4">
-        <v>2.22</v>
+        <v>377</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B220" s="4">
-        <v>4</v>
+        <v>379</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B221" s="4">
-        <v>-8.7</v>
+        <v>380</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B223" s="4">
-        <v>17.44</v>
+        <v>382</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B224" s="4">
-        <v>1.07</v>
+        <v>21</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B226" s="4">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="B227" s="4">
-        <v>16.7</v>
+        <v>386</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>85</v>
+        <v>387</v>
+      </c>
+      <c r="B228" s="4">
+        <v>7</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B229" s="4">
-        <v>1.74</v>
+        <v>388</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B230" s="4">
-        <v>0.81</v>
+        <v>4</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B232" s="4">
-        <v>12.2</v>
+        <v>2</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="B233" s="4">
-        <v>1.56</v>
+        <v>392</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B234" s="4" t="s">
-        <v>85</v>
+        <v>393</v>
+      </c>
+      <c r="B234" s="4">
+        <v>-46</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B236" s="4">
-        <v>23.3</v>
+        <v>-9</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B237" s="4">
-        <v>46.3</v>
+        <v>396</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B238" s="4">
-        <v>3.5</v>
+        <v>34</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="B239" s="4">
-        <v>33.1</v>
+        <v>398</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B240" s="4">
-        <v>0.9</v>
+        <v>33</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="B241" s="4">
-        <v>1</v>
+        <v>400</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B242" s="4">
-        <v>-2.6</v>
+        <v>21</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B243" s="4">
-        <v>-2.9</v>
+        <v>402</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B244" s="4">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="B245" s="4">
-        <v>13</v>
+        <v>404</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B246" s="4">
-        <v>13.1</v>
+        <v>9</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="B247" s="4">
-        <v>10.3</v>
+        <v>406</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B248" s="4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="B249" s="4">
-        <v>9.9</v>
+        <v>408</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="B250" s="4" t="s">
-        <v>33</v>
+        <v>409</v>
+      </c>
+      <c r="B250" s="4">
+        <v>15</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B251" s="4">
-        <v>-0.2</v>
+        <v>410</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B252" s="4">
-        <v>-3.7</v>
+        <v>11</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B254" s="4">
-        <v>-14.4</v>
+        <v>10</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="B255" s="4">
-        <v>8.3</v>
+        <v>414</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="B256" s="4" t="s">
-        <v>37</v>
+        <v>415</v>
+      </c>
+      <c r="B256" s="4">
+        <v>6</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B257" s="4">
-        <v>19.8</v>
+        <v>416</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B258" s="4">
-        <v>14.9</v>
+        <v>-31</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B260" s="4">
-        <v>16.7</v>
+        <v>98</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="B261" s="4">
-        <v>3.3</v>
+        <v>420</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="B262" s="4" t="s">
-        <v>40</v>
+        <v>421</v>
+      </c>
+      <c r="B262" s="4">
+        <v>33</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="B263" s="4">
-        <v>46.3</v>
+        <v>422</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B264" s="4">
-        <v>44.6</v>
+        <v>27</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B266" s="4">
-        <v>33.1</v>
+        <v>18</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="B267" s="4">
-        <v>23.7</v>
+        <v>426</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B268" s="4">
-        <v>18.6</v>
+        <v>14</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="B269" s="4">
-        <v>9.5</v>
+        <v>428</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B270" s="4">
-        <v>20.6</v>
+        <v>7</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B271" s="4">
-        <v>10.7</v>
+        <v>430</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B272" s="4">
-        <v>14.1</v>
+        <v>51</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="B273" s="4">
-        <v>22.7</v>
+        <v>432</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B274" s="4">
-        <v>9.5</v>
+        <v>27</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="B275" s="4">
-        <v>14.6</v>
+        <v>434</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B276" s="4">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B277" s="4">
-        <v>9.1</v>
+        <v>436</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B278" s="4">
-        <v>14.6</v>
+        <v>17</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B280" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="B281" s="4">
-        <v>11</v>
+        <v>440</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B282" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="B283" s="4">
-        <v>55</v>
+        <v>442</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B284" s="4">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="B285" s="4">
-        <v>60</v>
+        <v>444</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B286" s="4" t="s">
-        <v>8</v>
+        <v>445</v>
+      </c>
+      <c r="B286" s="4">
+        <v>5</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="B287" s="4">
-        <v>20.9</v>
+        <v>446</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B288" s="4">
-        <v>19.9</v>
+        <v>0.97</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B289" s="4">
-        <v>18.9</v>
+        <v>1.76</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="B290" s="4">
-        <v>19.7</v>
+        <v>449</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B291" s="4">
-        <v>28.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B292" s="4">
-        <v>24.6</v>
+        <v>-14.4</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B293" s="4">
-        <v>23.3</v>
+        <v>452</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="B294" s="4" t="s">
-        <v>34</v>
+        <v>453</v>
+      </c>
+      <c r="B294" s="4">
+        <v>-1.47</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B295" s="4">
-        <v>28.2</v>
+        <v>2.22</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B297" s="4">
-        <v>14.6</v>
+        <v>4</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="B298" s="4" t="s">
-        <v>37</v>
+        <v>457</v>
+      </c>
+      <c r="B298" s="4">
+        <v>-8.7</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="B299" s="4">
-        <v>14.8</v>
+        <v>458</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B300" s="4">
-        <v>8362.16</v>
+        <v>17.44</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B301" s="4">
-        <v>17.6</v>
+        <v>1.07</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="B302" s="4">
-        <v>7108.4</v>
+        <v>461</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="B303" s="4" t="s">
-        <v>35</v>
+        <v>462</v>
+      </c>
+      <c r="B303" s="4">
+        <v>6.1</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B304" s="4">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B306" s="4">
-        <v>23</v>
+        <v>1.74</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="B307" s="4" t="s">
-        <v>40</v>
+        <v>466</v>
+      </c>
+      <c r="B307" s="4">
+        <v>0.81</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="B308" s="4">
-        <v>21.4</v>
+        <v>467</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="B309" s="4" t="s">
-        <v>42</v>
+        <v>468</v>
+      </c>
+      <c r="B309" s="4">
+        <v>12.2</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B310" s="4">
-        <v>9</v>
+        <v>1.56</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="B311" s="4">
-        <v>12941</v>
+        <v>470</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="B312" s="4">
-        <v>58.4</v>
+        <v>471</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B313" s="4">
-        <v>36.3</v>
+        <v>23.3</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B314" s="4">
-        <v>5.3</v>
+        <v>46.3</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>33</v>
+        <v>474</v>
+      </c>
+      <c r="B315" s="4">
+        <v>3.5</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B316" s="4">
-        <v>65</v>
+        <v>33.1</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="B317" s="4" t="s">
-        <v>35</v>
+        <v>476</v>
+      </c>
+      <c r="B317" s="4">
+        <v>0.9</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B318" s="4">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="B319" s="4" t="s">
-        <v>38</v>
+        <v>478</v>
+      </c>
+      <c r="B319" s="4">
+        <v>-2.6</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B320" s="4">
-        <v>63</v>
+        <v>-2.9</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="B321" s="4" t="s">
-        <v>40</v>
+        <v>480</v>
+      </c>
+      <c r="B321" s="4">
+        <v>15.1</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B322" s="4">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="B323" s="4" t="s">
-        <v>43</v>
+        <v>482</v>
+      </c>
+      <c r="B323" s="4">
+        <v>13.1</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B324" s="4">
-        <v>48</v>
+        <v>10.3</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B325" s="4">
-        <v>13.4</v>
+        <v>10</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B326" s="4">
-        <v>13.2</v>
+        <v>9.9</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="B327" s="4">
-        <v>12.8</v>
+        <v>486</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B328" s="4">
-        <v>12.3</v>
+        <v>-0.2</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B329" s="4">
-        <v>180</v>
+        <v>-3.7</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B330" s="4">
+        <v>489</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B331" s="4">
+        <v>-14.4</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B332" s="4">
+        <v>8.3</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B334" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B335" s="4">
+        <v>14.9</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B337" s="4">
+        <v>16.7</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B338" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B340" s="4">
+        <v>46.3</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B341" s="4">
+        <v>44.6</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B343" s="4">
+        <v>33.1</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B344" s="4">
+        <v>23.7</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B345" s="4">
+        <v>18.6</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B346" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B347" s="4">
+        <v>20.6</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B348" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B349" s="4">
+        <v>14.1</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B350" s="4">
+        <v>22.7</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B351" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B352" s="4">
+        <v>14.6</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B353" s="4">
+        <v>20.4</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B354" s="4">
+        <v>9.1</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B355" s="4">
+        <v>14.6</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B357" s="4">
+        <v>20</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B358" s="4">
         <v>11</v>
       </c>
-      <c r="C330" s="4" t="s">
-        <v>161</v>
+      <c r="C358" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B359" s="4">
+        <v>9</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B360" s="4">
+        <v>55</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B361" s="4">
+        <v>58</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B362" s="4">
+        <v>60</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B364" s="4">
+        <v>20.9</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B365" s="4">
+        <v>19.9</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B366" s="4">
+        <v>18.9</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B367" s="4">
+        <v>19.7</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B368" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B369" s="4">
+        <v>24.6</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B370" s="4">
+        <v>23.3</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B372" s="4">
+        <v>28.2</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B374" s="4">
+        <v>14.6</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B376" s="4">
+        <v>14.8</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B377" s="4">
+        <v>8362.16</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B378" s="4">
+        <v>17.6</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="B379" s="4">
+        <v>7108.4</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="B381" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="B383" s="4">
+        <v>23</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B385" s="4">
+        <v>21.4</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B387" s="4">
+        <v>9</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B388" s="4">
+        <v>12941</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="B389" s="4">
+        <v>58.4</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B390" s="4">
+        <v>36.3</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B391" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B393" s="4">
+        <v>65</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="B395" s="4">
+        <v>43</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="B397" s="4">
+        <v>63</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B399" s="4">
+        <v>68</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B401" s="4">
+        <v>48</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B402" s="4">
+        <v>13.4</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B403" s="4">
+        <v>13.2</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B404" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B405" s="4">
+        <v>12.3</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B406" s="4">
+        <v>180</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="B407" s="4">
+        <v>11</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/output/Q1_2026_Earnings_Dashboard.xlsx
+++ b/output/Q1_2026_Earnings_Dashboard.xlsx
@@ -24,10 +24,38 @@
     <author>Author</author>
   </authors>
   <commentList>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F6" authorId="0">
       <text>
         <r>
           <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 22</t>
         </r>
       </text>
     </comment>
@@ -38,7 +66,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="E7" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F7" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0">
       <text>
         <r>
           <t>Extracted via OCR from chart on page 20</t>
@@ -73,6 +115,13 @@
         </r>
       </text>
     </comment>
+    <comment ref="E9" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H9" authorId="0">
       <text>
         <r>
@@ -87,6 +136,13 @@
         </r>
       </text>
     </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H10" authorId="0">
       <text>
         <r>
@@ -94,10 +150,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="E11" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H11" authorId="0">
       <text>
         <r>
           <t>Extracted via OCR from chart on page 22</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
         </r>
       </text>
     </comment>
@@ -157,6 +227,13 @@
         </r>
       </text>
     </comment>
+    <comment ref="E15" authorId="0">
+      <text>
+        <r>
+          <t>Extracted via OCR from chart on page 17</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F15" authorId="0">
       <text>
         <r>
@@ -183,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="568">
   <si>
     <t>Summary — FactSet Key Metrics</t>
   </si>
@@ -668,7 +745,7 @@
     <t>meta.parsedAt</t>
   </si>
   <si>
-    <t>2026-04-28T05:26:13.541Z</t>
+    <t>2026-04-28T16:29:23.344Z</t>
   </si>
   <si>
     <t>meta.pageCount</t>
@@ -761,30 +838,30 @@
     <t>sectorMatrix[0].epsBeatPct</t>
   </si>
   <si>
+    <t>sectorMatrix[0].revBeatPct</t>
+  </si>
+  <si>
+    <t>sectorMatrix[0].epsSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrix[0].revSurprise</t>
+  </si>
+  <si>
+    <t>sectorMatrix[0].earningsGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrix[0].revenueGrowth</t>
+  </si>
+  <si>
+    <t>sectorMatrix[0].netProfitMargin</t>
+  </si>
+  <si>
+    <t>sectorMatrix[0].netProfitMargin5yr</t>
+  </si>
+  <si>
     <t>object</t>
   </si>
   <si>
-    <t>sectorMatrix[0].revBeatPct</t>
-  </si>
-  <si>
-    <t>sectorMatrix[0].epsSurprise</t>
-  </si>
-  <si>
-    <t>sectorMatrix[0].revSurprise</t>
-  </si>
-  <si>
-    <t>sectorMatrix[0].earningsGrowth</t>
-  </si>
-  <si>
-    <t>sectorMatrix[0].revenueGrowth</t>
-  </si>
-  <si>
-    <t>sectorMatrix[0].netProfitMargin</t>
-  </si>
-  <si>
-    <t>sectorMatrix[0].netProfitMargin5yr</t>
-  </si>
-  <si>
     <t>sectorMatrix[0].netProfitMarginYearAgo</t>
   </si>
   <si>
@@ -1091,6 +1168,9 @@
     <t>sectorMatrixSource.Communication Services.epsBeatPct</t>
   </si>
   <si>
+    <t>chart-p16</t>
+  </si>
+  <si>
     <t>sectorMatrixSource.Communication Services.revBeatPct</t>
   </si>
   <si>
@@ -1103,6 +1183,9 @@
     <t>sectorMatrixSource.Communication Services.revSurprise</t>
   </si>
   <si>
+    <t>chart-p17</t>
+  </si>
+  <si>
     <t>sectorMatrixSource.Communication Services.earningsGrowth</t>
   </si>
   <si>
@@ -1136,6 +1219,9 @@
     <t>sectorMatrixSource.Consumer Discretionary.netProfitMargin</t>
   </si>
   <si>
+    <t>chart-p22</t>
+  </si>
+  <si>
     <t>sectorMatrixSource.Consumer Staples.epsBeatPct</t>
   </si>
   <si>
@@ -1145,9 +1231,6 @@
     <t>sectorMatrixSource.Consumer Staples.epsSurprise</t>
   </si>
   <si>
-    <t>chart-p17</t>
-  </si>
-  <si>
     <t>sectorMatrixSource.Consumer Staples.revSurprise</t>
   </si>
   <si>
@@ -1158,9 +1241,6 @@
   </si>
   <si>
     <t>sectorMatrixSource.Consumer Staples.netProfitMargin</t>
-  </si>
-  <si>
-    <t>chart-p22</t>
   </si>
   <si>
     <t>sectorMatrixSource.Energy.epsBeatPct</t>
@@ -2678,8 +2758,8 @@
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
+      <c r="B5" s="4">
+        <v>75</v>
       </c>
       <c r="C5" s="4">
         <v>100</v>
@@ -2687,8 +2767,8 @@
       <c r="D5" s="4">
         <v>20.6</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
+      <c r="E5" s="6">
+        <v>1.6</v>
       </c>
       <c r="F5" s="4">
         <v>-0.2</v>
@@ -2716,8 +2796,8 @@
       <c r="C6" s="4">
         <v>69</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
+      <c r="D6" s="6">
+        <v>7.7</v>
       </c>
       <c r="E6" s="4">
         <v>0.4</v>
@@ -2725,11 +2805,11 @@
       <c r="F6" s="6">
         <v>2.4</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>8</v>
+      <c r="G6" s="6">
+        <v>8.3</v>
+      </c>
+      <c r="H6" s="6">
+        <v>8.2</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>8</v>
@@ -2742,8 +2822,8 @@
       <c r="A7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
+      <c r="B7" s="4">
+        <v>78</v>
       </c>
       <c r="C7" s="4">
         <v>100</v>
@@ -2751,14 +2831,14 @@
       <c r="D7" s="6">
         <v>3</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
+      <c r="E7" s="6">
+        <v>1.5</v>
       </c>
       <c r="F7" s="6">
         <v>2.7</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>8</v>
+      <c r="G7" s="6">
+        <v>7.1</v>
       </c>
       <c r="H7" s="6">
         <v>5.9</v>
@@ -2806,17 +2886,17 @@
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
+      <c r="B9" s="4">
+        <v>85</v>
+      </c>
+      <c r="C9" s="4">
+        <v>70</v>
       </c>
       <c r="D9" s="6">
         <v>6.7</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>8</v>
+      <c r="E9" s="6">
+        <v>1.2</v>
       </c>
       <c r="F9" s="4">
         <v>19.8</v>
@@ -2841,14 +2921,14 @@
       <c r="B10" s="4">
         <v>100</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
+      <c r="C10" s="4">
+        <v>92</v>
       </c>
       <c r="D10" s="6">
         <v>5.7</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
+      <c r="E10" s="6">
+        <v>1.9</v>
       </c>
       <c r="F10" s="4">
         <v>-8.7</v>
@@ -2870,17 +2950,17 @@
       <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
+      <c r="B11" s="4">
+        <v>76</v>
+      </c>
+      <c r="C11" s="4">
+        <v>76</v>
       </c>
       <c r="D11" s="4">
         <v>33.2</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>8</v>
+      <c r="E11" s="6">
+        <v>2</v>
       </c>
       <c r="F11" s="4">
         <v>16.7</v>
@@ -2905,14 +2985,14 @@
       <c r="B12" s="4">
         <v>93</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
+      <c r="C12" s="4">
+        <v>93</v>
       </c>
       <c r="D12" s="4">
         <v>21.1</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>8</v>
+      <c r="E12" s="6">
+        <v>5.8</v>
       </c>
       <c r="F12" s="4">
         <v>46.3</v>
@@ -2934,11 +3014,11 @@
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>8</v>
+      <c r="B13" s="4">
+        <v>83</v>
+      </c>
+      <c r="C13" s="4">
+        <v>83</v>
       </c>
       <c r="D13" s="4">
         <v>28.5</v>
@@ -3007,8 +3087,8 @@
       <c r="D15" s="6">
         <v>5.8</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>8</v>
+      <c r="E15" s="6">
+        <v>1.1</v>
       </c>
       <c r="F15" s="6">
         <v>11.9</v>
@@ -3071,7 +3151,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8D0FC7D1-8456-46CC-B03F-45C241E02ECA}</x14:id>
+          <x14:id>{F3F664E3-5044-49A4-955B-A1F539B84DB8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3085,7 +3165,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55366F1E-A9FD-4AC6-81FA-3653FA117B07}</x14:id>
+          <x14:id>{8E63E2C1-D79E-4A51-9396-1C43A0223192}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3099,7 +3179,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{075E4C2A-3FB0-4F06-AFDA-F09C6ACDB2B1}</x14:id>
+          <x14:id>{5935779A-6A31-48B3-95D7-ACC5E2E18713}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3113,7 +3193,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9329AF12-238B-49C3-A081-DFCBA2CA4D43}</x14:id>
+          <x14:id>{C1045BA5-C1A9-40E6-86B2-1A3E9DFD1C19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3127,7 +3207,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5DBB4FA6-F4D4-4F83-9B32-029A67ABEF2B}</x14:id>
+          <x14:id>{D1B99D3A-7C72-491C-9644-921A1AFA9FF8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3141,7 +3221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A996EF0C-CF84-4497-A21A-AF0DCDF2CD18}</x14:id>
+          <x14:id>{DE9C98B8-EBBB-428A-A8DF-B00D4F2D8579}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3155,7 +3235,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3693E62-54D1-4D55-8BCA-AD9F84A25AC3}</x14:id>
+          <x14:id>{87AAB902-AE68-4734-B91A-321860973BB2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3169,7 +3249,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1E072F38-9FB1-4711-ABA1-50DD73538191}</x14:id>
+          <x14:id>{7BE4F1BE-9360-4CD8-8DCE-29B8AA29DEF8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3183,7 +3263,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CCD2DD5E-484A-4EF1-9DAF-F607CD37D61C}</x14:id>
+          <x14:id>{761B4007-759B-481D-9B0E-B3F67BEDEA31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3194,7 +3274,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8D0FC7D1-8456-46CC-B03F-45C241E02ECA}">
+          <x14:cfRule type="dataBar" id="{F3F664E3-5044-49A4-955B-A1F539B84DB8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3203,7 +3283,7 @@
           <xm:sqref>B5:B15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55366F1E-A9FD-4AC6-81FA-3653FA117B07}">
+          <x14:cfRule type="dataBar" id="{8E63E2C1-D79E-4A51-9396-1C43A0223192}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3212,7 +3292,7 @@
           <xm:sqref>C5:C15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{075E4C2A-3FB0-4F06-AFDA-F09C6ACDB2B1}">
+          <x14:cfRule type="dataBar" id="{5935779A-6A31-48B3-95D7-ACC5E2E18713}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3221,7 +3301,7 @@
           <xm:sqref>D5:D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9329AF12-238B-49C3-A081-DFCBA2CA4D43}">
+          <x14:cfRule type="dataBar" id="{C1045BA5-C1A9-40E6-86B2-1A3E9DFD1C19}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3230,7 +3310,7 @@
           <xm:sqref>E5:E15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5DBB4FA6-F4D4-4F83-9B32-029A67ABEF2B}">
+          <x14:cfRule type="dataBar" id="{D1B99D3A-7C72-491C-9644-921A1AFA9FF8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3239,7 +3319,7 @@
           <xm:sqref>F5:F15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A996EF0C-CF84-4497-A21A-AF0DCDF2CD18}">
+          <x14:cfRule type="dataBar" id="{DE9C98B8-EBBB-428A-A8DF-B00D4F2D8579}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3248,7 +3328,7 @@
           <xm:sqref>G5:G15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3693E62-54D1-4D55-8BCA-AD9F84A25AC3}">
+          <x14:cfRule type="dataBar" id="{87AAB902-AE68-4734-B91A-321860973BB2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3257,7 +3337,7 @@
           <xm:sqref>H5:H15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1E072F38-9FB1-4711-ABA1-50DD73538191}">
+          <x14:cfRule type="dataBar" id="{7BE4F1BE-9360-4CD8-8DCE-29B8AA29DEF8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3266,7 +3346,7 @@
           <xm:sqref>I5:I15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CCD2DD5E-484A-4EF1-9DAF-F607CD37D61C}">
+          <x14:cfRule type="dataBar" id="{761B4007-759B-481D-9B0E-B3F67BEDEA31}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3863,7 +3943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88D5E966-A3B9-4D66-BF2A-2B643B4538FC}</x14:id>
+          <x14:id>{4C60523F-D812-44E0-8E01-0B865EB973E9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3874,7 +3954,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88D5E966-A3B9-4D66-BF2A-2B643B4538FC}">
+          <x14:cfRule type="dataBar" id="{4C60523F-D812-44E0-8E01-0B865EB973E9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -4430,7 +4510,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78F4E6A3-F20D-4668-A68B-B0BD4FCB65E2}</x14:id>
+          <x14:id>{DE88097B-1325-49A7-BEE4-B465C9A24D3E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4444,7 +4524,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3EF8189F-EDB4-4252-B25A-E90BEE6A584F}</x14:id>
+          <x14:id>{1EA392E8-C449-4F76-A672-71019A5E40AF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4458,7 +4538,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F9E625A1-AFB2-42B2-B718-011102F69CEA}</x14:id>
+          <x14:id>{4FEEE8BB-1194-493E-9925-B419A51927B1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4469,7 +4549,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78F4E6A3-F20D-4668-A68B-B0BD4FCB65E2}">
+          <x14:cfRule type="dataBar" id="{DE88097B-1325-49A7-BEE4-B465C9A24D3E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -4478,7 +4558,7 @@
           <xm:sqref>B11:B21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3EF8189F-EDB4-4252-B25A-E90BEE6A584F}">
+          <x14:cfRule type="dataBar" id="{1EA392E8-C449-4F76-A672-71019A5E40AF}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -4487,7 +4567,7 @@
           <xm:sqref>C11:C21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F9E625A1-AFB2-42B2-B718-011102F69CEA}">
+          <x14:cfRule type="dataBar" id="{4FEEE8BB-1194-493E-9925-B419A51927B1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -5737,7 +5817,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A6C52E82-D275-4B44-92FE-4E311EBBB9A9}</x14:id>
+          <x14:id>{BF6A22B3-30BF-4531-8FCC-E792ED68FC28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5751,7 +5831,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62764D28-F051-46D1-A12A-436F2056CBE7}</x14:id>
+          <x14:id>{F22CAC82-CD2F-4E1B-9522-12A5E6F0282D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5765,7 +5845,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CB51F138-8304-4341-BA04-BE514D943690}</x14:id>
+          <x14:id>{388514A5-CC1B-471A-AA39-DCADDAFD5464}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5776,7 +5856,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A6C52E82-D275-4B44-92FE-4E311EBBB9A9}">
+          <x14:cfRule type="dataBar" id="{BF6A22B3-30BF-4531-8FCC-E792ED68FC28}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -5785,7 +5865,7 @@
           <xm:sqref>B11:B21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62764D28-F051-46D1-A12A-436F2056CBE7}">
+          <x14:cfRule type="dataBar" id="{F22CAC82-CD2F-4E1B-9522-12A5E6F0282D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -5794,7 +5874,7 @@
           <xm:sqref>B30:B40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CB51F138-8304-4341-BA04-BE514D943690}">
+          <x14:cfRule type="dataBar" id="{388514A5-CC1B-471A-AA39-DCADDAFD5464}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -6208,16 +6288,16 @@
       <c r="A37" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>8</v>
+      <c r="B37" s="4">
+        <v>75</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="4">
         <v>100</v>
@@ -6228,7 +6308,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B39" s="4">
         <v>20.6</v>
@@ -6239,18 +6319,18 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>8</v>
+        <v>194</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1.6</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="4">
         <v>-0.2</v>
@@ -6261,7 +6341,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B42" s="4">
         <v>13.2</v>
@@ -6272,7 +6352,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B43" s="4">
         <v>14.1</v>
@@ -6283,13 +6363,13 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -6340,11 +6420,11 @@
       <c r="A49" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>8</v>
+      <c r="B49" s="4">
+        <v>7.7</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -6373,22 +6453,22 @@
       <c r="A52" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>8</v>
+      <c r="B52" s="4">
+        <v>8.3</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>8</v>
+      <c r="B53" s="4">
+        <v>8.2</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -6399,7 +6479,7 @@
         <v>8</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -6410,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -6428,11 +6508,11 @@
       <c r="A57" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>8</v>
+      <c r="B57" s="4">
+        <v>78</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -6461,11 +6541,11 @@
       <c r="A60" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>8</v>
+      <c r="B60" s="4">
+        <v>1.5</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -6483,11 +6563,11 @@
       <c r="A62" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>8</v>
+      <c r="B62" s="4">
+        <v>7.1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -6509,7 +6589,7 @@
         <v>8</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -6520,7 +6600,7 @@
         <v>8</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -6630,7 +6710,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -6648,22 +6728,22 @@
       <c r="A77" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>8</v>
+      <c r="B77" s="4">
+        <v>85</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>8</v>
+      <c r="B78" s="4">
+        <v>70</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -6681,11 +6761,11 @@
       <c r="A80" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>8</v>
+      <c r="B80" s="4">
+        <v>1.2</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -6729,7 +6809,7 @@
         <v>8</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -6740,7 +6820,7 @@
         <v>8</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -6769,11 +6849,11 @@
       <c r="A88" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>8</v>
+      <c r="B88" s="4">
+        <v>92</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -6791,11 +6871,11 @@
       <c r="A90" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>8</v>
+      <c r="B90" s="4">
+        <v>1.9</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -6839,7 +6919,7 @@
         <v>8</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -6850,7 +6930,7 @@
         <v>8</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -6868,22 +6948,22 @@
       <c r="A97" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>8</v>
+      <c r="B97" s="4">
+        <v>76</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>8</v>
+      <c r="B98" s="4">
+        <v>76</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -6901,11 +6981,11 @@
       <c r="A100" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B100" s="4" t="s">
-        <v>8</v>
+      <c r="B100" s="4">
+        <v>2</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -6949,7 +7029,7 @@
         <v>8</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -6960,7 +7040,7 @@
         <v>8</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -6989,11 +7069,11 @@
       <c r="A108" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B108" s="4" t="s">
-        <v>8</v>
+      <c r="B108" s="4">
+        <v>93</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -7011,11 +7091,11 @@
       <c r="A110" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>8</v>
+      <c r="B110" s="4">
+        <v>5.8</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -7088,22 +7168,22 @@
       <c r="A117" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B117" s="4" t="s">
-        <v>8</v>
+      <c r="B117" s="4">
+        <v>83</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B118" s="4" t="s">
-        <v>8</v>
+      <c r="B118" s="4">
+        <v>83</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -7169,7 +7249,7 @@
         <v>8</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -7180,7 +7260,7 @@
         <v>8</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -7279,7 +7359,7 @@
         <v>8</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -7290,7 +7370,7 @@
         <v>8</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -7341,11 +7421,11 @@
       <c r="A140" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>8</v>
+      <c r="B140" s="4">
+        <v>1.1</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -7389,7 +7469,7 @@
         <v>8</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -7400,7 +7480,7 @@
         <v>8</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -7408,18 +7488,18 @@
         <v>301</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>155</v>
@@ -7427,10 +7507,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>155</v>
@@ -7438,21 +7518,21 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>155</v>
@@ -7460,10 +7540,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>155</v>
@@ -7471,10 +7551,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>155</v>
@@ -7482,10 +7562,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>155</v>
@@ -7493,10 +7573,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>155</v>
@@ -7504,21 +7584,21 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>155</v>
@@ -7526,10 +7606,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>155</v>
@@ -7537,43 +7617,43 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>8</v>
+        <v>316</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>8</v>
+        <v>319</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>155</v>
@@ -7581,10 +7661,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>155</v>
@@ -7592,21 +7672,21 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>155</v>
@@ -7614,21 +7694,21 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>8</v>
+        <v>316</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>155</v>
@@ -7636,10 +7716,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>155</v>
@@ -7647,10 +7727,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>155</v>
@@ -7658,10 +7738,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>155</v>
@@ -7669,10 +7749,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>155</v>
@@ -7680,10 +7760,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>155</v>
@@ -7691,10 +7771,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>155</v>
@@ -7702,10 +7782,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>155</v>
@@ -7713,32 +7793,32 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>155</v>
@@ -7746,21 +7826,21 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>155</v>
@@ -7768,10 +7848,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>155</v>
@@ -7779,10 +7859,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>155</v>
@@ -7790,10 +7870,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>155</v>
@@ -7801,21 +7881,21 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>155</v>
@@ -7823,21 +7903,21 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>155</v>
@@ -7845,10 +7925,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>155</v>
@@ -7856,10 +7936,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>155</v>
@@ -7867,32 +7947,32 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>155</v>
@@ -7900,21 +7980,21 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>155</v>
@@ -7922,10 +8002,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>155</v>
@@ -7933,10 +8013,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>155</v>
@@ -7944,10 +8024,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>155</v>
@@ -7955,21 +8035,21 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>155</v>
@@ -7977,21 +8057,21 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>155</v>
@@ -7999,10 +8079,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>155</v>
@@ -8010,10 +8090,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>155</v>
@@ -8021,32 +8101,32 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>155</v>
@@ -8054,10 +8134,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>155</v>
@@ -8065,10 +8145,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>155</v>
@@ -8076,10 +8156,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>155</v>
@@ -8087,10 +8167,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>155</v>
@@ -8098,10 +8178,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>155</v>
@@ -8109,10 +8189,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>155</v>
@@ -8120,10 +8200,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>155</v>
@@ -8131,10 +8211,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>155</v>
@@ -8142,10 +8222,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>155</v>
@@ -8153,10 +8233,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>155</v>
@@ -8164,10 +8244,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>155</v>
@@ -8175,10 +8255,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>155</v>
@@ -8186,10 +8266,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>155</v>
@@ -8197,10 +8277,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>155</v>
@@ -8208,21 +8288,21 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>155</v>
@@ -8230,10 +8310,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>155</v>
@@ -8241,10 +8321,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>155</v>
@@ -8252,7 +8332,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>50</v>
@@ -8263,7 +8343,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B224" s="4">
         <v>21</v>
@@ -8274,7 +8354,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>52</v>
@@ -8285,7 +8365,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B226" s="4">
         <v>10</v>
@@ -8296,7 +8376,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>53</v>
@@ -8307,7 +8387,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B228" s="4">
         <v>7</v>
@@ -8318,7 +8398,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>54</v>
@@ -8329,7 +8409,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B230" s="4">
         <v>4</v>
@@ -8340,7 +8420,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>55</v>
@@ -8351,7 +8431,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B232" s="4">
         <v>2</v>
@@ -8362,7 +8442,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>57</v>
@@ -8373,7 +8453,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B234" s="4">
         <v>-46</v>
@@ -8384,7 +8464,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>59</v>
@@ -8395,7 +8475,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B236" s="4">
         <v>-9</v>
@@ -8406,7 +8486,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>60</v>
@@ -8417,7 +8497,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B238" s="4">
         <v>34</v>
@@ -8428,7 +8508,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>61</v>
@@ -8439,7 +8519,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B240" s="4">
         <v>33</v>
@@ -8450,7 +8530,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>62</v>
@@ -8461,7 +8541,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B242" s="4">
         <v>21</v>
@@ -8472,7 +8552,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>63</v>
@@ -8483,7 +8563,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B244" s="4">
         <v>16</v>
@@ -8494,7 +8574,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>64</v>
@@ -8505,7 +8585,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B246" s="4">
         <v>9</v>
@@ -8516,7 +8596,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>61</v>
@@ -8527,7 +8607,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B248" s="4">
         <v>23</v>
@@ -8538,7 +8618,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>62</v>
@@ -8549,7 +8629,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B250" s="4">
         <v>15</v>
@@ -8560,7 +8640,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>64</v>
@@ -8571,7 +8651,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B252" s="4">
         <v>11</v>
@@ -8582,7 +8662,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>63</v>
@@ -8593,7 +8673,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B254" s="4">
         <v>10</v>
@@ -8604,7 +8684,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>60</v>
@@ -8615,7 +8695,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B256" s="4">
         <v>6</v>
@@ -8626,7 +8706,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>65</v>
@@ -8637,7 +8717,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B258" s="4">
         <v>-31</v>
@@ -8648,7 +8728,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>66</v>
@@ -8659,7 +8739,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B260" s="4">
         <v>98</v>
@@ -8670,7 +8750,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>67</v>
@@ -8681,7 +8761,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B262" s="4">
         <v>33</v>
@@ -8692,7 +8772,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B263" s="4" t="s">
         <v>68</v>
@@ -8703,7 +8783,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B264" s="4">
         <v>27</v>
@@ -8714,7 +8794,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B265" s="4" t="s">
         <v>69</v>
@@ -8725,7 +8805,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B266" s="4">
         <v>18</v>
@@ -8736,7 +8816,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B267" s="4" t="s">
         <v>33</v>
@@ -8747,7 +8827,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B268" s="4">
         <v>14</v>
@@ -8758,7 +8838,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B269" s="4" t="s">
         <v>70</v>
@@ -8769,7 +8849,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B270" s="4">
         <v>7</v>
@@ -8780,7 +8860,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B271" s="4" t="s">
         <v>66</v>
@@ -8791,7 +8871,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B272" s="4">
         <v>51</v>
@@ -8802,7 +8882,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B273" s="4" t="s">
         <v>68</v>
@@ -8813,7 +8893,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B274" s="4">
         <v>27</v>
@@ -8824,7 +8904,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B275" s="4" t="s">
         <v>67</v>
@@ -8835,7 +8915,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B276" s="4">
         <v>21</v>
@@ -8846,7 +8926,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B277" s="4" t="s">
         <v>69</v>
@@ -8857,7 +8937,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B278" s="4">
         <v>17</v>
@@ -8868,7 +8948,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B279" s="4" t="s">
         <v>71</v>
@@ -8879,7 +8959,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B280" s="4">
         <v>14</v>
@@ -8890,7 +8970,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B281" s="4" t="s">
         <v>70</v>
@@ -8901,7 +8981,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B282" s="4">
         <v>8</v>
@@ -8912,7 +8992,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B283" s="4" t="s">
         <v>72</v>
@@ -8923,7 +9003,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B284" s="4">
         <v>133</v>
@@ -8934,7 +9014,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B285" s="4" t="s">
         <v>73</v>
@@ -8945,7 +9025,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B286" s="4">
         <v>5</v>
@@ -8956,7 +9036,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B287" s="4" t="s">
         <v>81</v>
@@ -8967,7 +9047,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B288" s="4">
         <v>0.97</v>
@@ -8978,7 +9058,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B289" s="4">
         <v>1.76</v>
@@ -8989,7 +9069,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B290" s="4" t="s">
         <v>81</v>
@@ -9000,7 +9080,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B291" s="4">
         <v>-0.2</v>
@@ -9011,7 +9091,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B292" s="4">
         <v>-14.4</v>
@@ -9022,7 +9102,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B293" s="4" t="s">
         <v>83</v>
@@ -9033,7 +9113,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B294" s="4">
         <v>-1.47</v>
@@ -9044,7 +9124,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B295" s="4">
         <v>2.22</v>
@@ -9055,7 +9135,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B296" s="4" t="s">
         <v>83</v>
@@ -9066,7 +9146,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B297" s="4">
         <v>4</v>
@@ -9077,7 +9157,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B298" s="4">
         <v>-8.7</v>
@@ -9088,7 +9168,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>85</v>
@@ -9099,7 +9179,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B300" s="4">
         <v>17.44</v>
@@ -9110,7 +9190,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B301" s="4">
         <v>1.07</v>
@@ -9121,7 +9201,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>85</v>
@@ -9132,7 +9212,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B303" s="4">
         <v>6.1</v>
@@ -9143,7 +9223,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B304" s="4">
         <v>16.7</v>
@@ -9154,7 +9234,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>87</v>
@@ -9165,7 +9245,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B306" s="4">
         <v>1.74</v>
@@ -9176,7 +9256,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B307" s="4">
         <v>0.81</v>
@@ -9187,7 +9267,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>89</v>
@@ -9198,7 +9278,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B309" s="4">
         <v>12.2</v>
@@ -9209,7 +9289,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B310" s="4">
         <v>1.56</v>
@@ -9220,7 +9300,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>87</v>
@@ -9231,7 +9311,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>89</v>
@@ -9242,7 +9322,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B313" s="4">
         <v>23.3</v>
@@ -9253,7 +9333,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B314" s="4">
         <v>46.3</v>
@@ -9264,7 +9344,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B315" s="4">
         <v>3.5</v>
@@ -9275,7 +9355,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B316" s="4">
         <v>33.1</v>
@@ -9286,7 +9366,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B317" s="4">
         <v>0.9</v>
@@ -9297,7 +9377,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B318" s="4">
         <v>1</v>
@@ -9308,7 +9388,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B319" s="4">
         <v>-2.6</v>
@@ -9319,7 +9399,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B320" s="4">
         <v>-2.9</v>
@@ -9330,7 +9410,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B321" s="4">
         <v>15.1</v>
@@ -9341,7 +9421,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B322" s="4">
         <v>13</v>
@@ -9352,7 +9432,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B323" s="4">
         <v>13.1</v>
@@ -9363,7 +9443,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B324" s="4">
         <v>10.3</v>
@@ -9374,7 +9454,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B325" s="4">
         <v>10</v>
@@ -9385,7 +9465,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B326" s="4">
         <v>9.9</v>
@@ -9396,7 +9476,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B327" s="4" t="s">
         <v>33</v>
@@ -9407,7 +9487,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B328" s="4">
         <v>-0.2</v>
@@ -9418,7 +9498,7 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B329" s="4">
         <v>-3.7</v>
@@ -9429,7 +9509,7 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B330" s="4" t="s">
         <v>36</v>
@@ -9440,7 +9520,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B331" s="4">
         <v>-14.4</v>
@@ -9451,7 +9531,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B332" s="4">
         <v>8.3</v>
@@ -9462,7 +9542,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B333" s="4" t="s">
         <v>37</v>
@@ -9473,7 +9553,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B334" s="4">
         <v>19.8</v>
@@ -9484,7 +9564,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B335" s="4">
         <v>14.9</v>
@@ -9495,7 +9575,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B336" s="4" t="s">
         <v>39</v>
@@ -9506,7 +9586,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B337" s="4">
         <v>16.7</v>
@@ -9517,7 +9597,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B338" s="4">
         <v>3.3</v>
@@ -9528,7 +9608,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>40</v>
@@ -9539,7 +9619,7 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B340" s="4">
         <v>46.3</v>
@@ -9550,7 +9630,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B341" s="4">
         <v>44.6</v>
@@ -9561,7 +9641,7 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B342" s="4" t="s">
         <v>41</v>
@@ -9572,7 +9652,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B343" s="4">
         <v>33.1</v>
@@ -9583,7 +9663,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B344" s="4">
         <v>23.7</v>
@@ -9594,7 +9674,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B345" s="4">
         <v>18.6</v>
@@ -9605,7 +9685,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B346" s="4">
         <v>9.5</v>
@@ -9616,7 +9696,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B347" s="4">
         <v>20.6</v>
@@ -9627,7 +9707,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B348" s="4">
         <v>10.7</v>
@@ -9638,7 +9718,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B349" s="4">
         <v>14.1</v>
@@ -9649,7 +9729,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B350" s="4">
         <v>22.7</v>
@@ -9660,7 +9740,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B351" s="4">
         <v>9.5</v>
@@ -9671,7 +9751,7 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B352" s="4">
         <v>14.6</v>
@@ -9682,7 +9762,7 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B353" s="4">
         <v>20.4</v>
@@ -9693,7 +9773,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B354" s="4">
         <v>9.1</v>
@@ -9704,7 +9784,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B355" s="4">
         <v>14.6</v>
@@ -9715,7 +9795,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B356" s="4" t="s">
         <v>113</v>
@@ -9726,7 +9806,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B357" s="4">
         <v>20</v>
@@ -9737,7 +9817,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B358" s="4">
         <v>11</v>
@@ -9748,7 +9828,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B359" s="4">
         <v>9</v>
@@ -9759,7 +9839,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B360" s="4">
         <v>55</v>
@@ -9770,7 +9850,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B361" s="4">
         <v>58</v>
@@ -9781,7 +9861,7 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B362" s="4">
         <v>60</v>
@@ -9792,18 +9872,18 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B363" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B364" s="4">
         <v>20.9</v>
@@ -9814,7 +9894,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B365" s="4">
         <v>19.9</v>
@@ -9825,7 +9905,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B366" s="4">
         <v>18.9</v>
@@ -9836,7 +9916,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B367" s="4">
         <v>19.7</v>
@@ -9847,7 +9927,7 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B368" s="4">
         <v>28.1</v>
@@ -9858,7 +9938,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B369" s="4">
         <v>24.6</v>
@@ -9869,7 +9949,7 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B370" s="4">
         <v>23.3</v>
@@ -9880,7 +9960,7 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B371" s="4" t="s">
         <v>34</v>
@@ -9891,7 +9971,7 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B372" s="4">
         <v>28.2</v>
@@ -9902,7 +9982,7 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B373" s="4" t="s">
         <v>36</v>
@@ -9913,7 +9993,7 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B374" s="4">
         <v>14.6</v>
@@ -9924,7 +10004,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B375" s="4" t="s">
         <v>37</v>
@@ -9935,7 +10015,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B376" s="4">
         <v>14.8</v>
@@ -9946,7 +10026,7 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B377" s="4">
         <v>8362.16</v>
@@ -9957,7 +10037,7 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B378" s="4">
         <v>17.6</v>
@@ -9968,7 +10048,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B379" s="4">
         <v>7108.4</v>
@@ -9979,7 +10059,7 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B380" s="4" t="s">
         <v>35</v>
@@ -9990,7 +10070,7 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B381" s="4">
         <v>10.4</v>
@@ -10001,7 +10081,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B382" s="4" t="s">
         <v>38</v>
@@ -10012,7 +10092,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B383" s="4">
         <v>23</v>
@@ -10023,7 +10103,7 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B384" s="4" t="s">
         <v>40</v>
@@ -10034,7 +10114,7 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B385" s="4">
         <v>21.4</v>
@@ -10045,7 +10125,7 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B386" s="4" t="s">
         <v>42</v>
@@ -10056,7 +10136,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B387" s="4">
         <v>9</v>
@@ -10067,7 +10147,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B388" s="4">
         <v>12941</v>
@@ -10078,7 +10158,7 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B389" s="4">
         <v>58.4</v>
@@ -10089,7 +10169,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B390" s="4">
         <v>36.3</v>
@@ -10100,7 +10180,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B391" s="4">
         <v>5.3</v>
@@ -10111,7 +10191,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B392" s="4" t="s">
         <v>33</v>
@@ -10122,7 +10202,7 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B393" s="4">
         <v>65</v>
@@ -10133,7 +10213,7 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B394" s="4" t="s">
         <v>35</v>
@@ -10144,7 +10224,7 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B395" s="4">
         <v>43</v>
@@ -10155,7 +10235,7 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B396" s="4" t="s">
         <v>38</v>
@@ -10166,7 +10246,7 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B397" s="4">
         <v>63</v>
@@ -10177,7 +10257,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B398" s="4" t="s">
         <v>40</v>
@@ -10188,7 +10268,7 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B399" s="4">
         <v>68</v>
@@ -10199,7 +10279,7 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B400" s="4" t="s">
         <v>43</v>
@@ -10210,7 +10290,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B401" s="4">
         <v>48</v>
@@ -10221,7 +10301,7 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B402" s="4">
         <v>13.4</v>
@@ -10232,7 +10312,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B403" s="4">
         <v>13.2</v>
@@ -10243,7 +10323,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B404" s="4">
         <v>12.8</v>
@@ -10254,7 +10334,7 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B405" s="4">
         <v>12.3</v>
@@ -10265,7 +10345,7 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B406" s="4">
         <v>180</v>
@@ -10276,7 +10356,7 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B407" s="4">
         <v>11</v>
